--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2021_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2021_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:21</t>
+    <t xml:space="preserve">2026-09-09 23:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2021_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2021_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:17</t>
+    <t xml:space="preserve">2026-09-17 14:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2021_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2021_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:13</t>
+    <t xml:space="preserve">2026-09-23 12:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1500,7 +1500,9 @@
       <c r="C53" s="2" t="n">
         <v>13303</v>
       </c>
-      <c r="D53" s="2"/>
+      <c r="D53" s="2" t="n">
+        <v>2021</v>
+      </c>
       <c r="E53" s="2"/>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2021_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2021_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:42</t>
+    <t xml:space="preserve">2026-10-02 15:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_median_a_2021_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_median_a_2021_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:03</t>
+    <t xml:space="preserve">2026-10-05 11:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
